--- a/downloads/karnataka.xlsx
+++ b/downloads/karnataka.xlsx
@@ -12,7 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Names left off by district" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft roll by district and sex" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roll of 25 September 2026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roll of 9 October 2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notices to 9 October 2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms 6, 6A, 7 and 8 to 8 Octob" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -623,6 +626,99 @@
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>in this workbook only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Roll of 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Source table</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>The roll of 9 October 2026, by district and sex.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>in this workbook only</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Source table</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Notices generated, delivered and heard by 9 October 2026, by district.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>in this workbook only</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Source table</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Forms received from 16 June to 8 October 2026, by district.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>in this workbook only</t>
         </is>
@@ -652,7 +748,7 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -709,7 +805,7 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>roll_25_sep_2026</t>
+          <t>roll_9_oct_2026</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
@@ -752,10 +848,10 @@
         <v>1086756</v>
       </c>
       <c r="K2" t="n">
-        <v>1086749</v>
+        <v>1089133</v>
       </c>
       <c r="L2" t="n">
-        <v>49.33</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="3">
@@ -792,10 +888,10 @@
         <v>1029196</v>
       </c>
       <c r="K3" t="n">
-        <v>1030531</v>
+        <v>1048191</v>
       </c>
       <c r="L3" t="n">
-        <v>45.47</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="4">
@@ -832,10 +928,10 @@
         <v>1280085</v>
       </c>
       <c r="K4" t="n">
-        <v>1280895</v>
+        <v>1294917</v>
       </c>
       <c r="L4" t="n">
-        <v>45.09</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="5">
@@ -872,10 +968,10 @@
         <v>2303623</v>
       </c>
       <c r="K5" t="n">
-        <v>2303825</v>
+        <v>2317370</v>
       </c>
       <c r="L5" t="n">
-        <v>42.71</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="6">
@@ -912,10 +1008,10 @@
         <v>1849585</v>
       </c>
       <c r="K6" t="n">
-        <v>1854603</v>
+        <v>1869281</v>
       </c>
       <c r="L6" t="n">
-        <v>21.8</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="7">
@@ -952,10 +1048,10 @@
         <v>2242452</v>
       </c>
       <c r="K7" t="n">
-        <v>2247533</v>
+        <v>2263216</v>
       </c>
       <c r="L7" t="n">
-        <v>19.72</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="8">
@@ -992,10 +1088,10 @@
         <v>1393163</v>
       </c>
       <c r="K8" t="n">
-        <v>1407517</v>
+        <v>1420267</v>
       </c>
       <c r="L8" t="n">
-        <v>17.91</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="9">
@@ -1032,10 +1128,10 @@
         <v>1006307</v>
       </c>
       <c r="K9" t="n">
-        <v>1014439</v>
+        <v>1018758</v>
       </c>
       <c r="L9" t="n">
-        <v>17.5</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="10">
@@ -1072,10 +1168,10 @@
         <v>864005</v>
       </c>
       <c r="K10" t="n">
-        <v>864802</v>
+        <v>881633</v>
       </c>
       <c r="L10" t="n">
-        <v>17.89</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="11">
@@ -1112,10 +1208,10 @@
         <v>1353946</v>
       </c>
       <c r="K11" t="n">
-        <v>1357281</v>
+        <v>1367709</v>
       </c>
       <c r="L11" t="n">
-        <v>16.32</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="12">
@@ -1152,10 +1248,10 @@
         <v>1220916</v>
       </c>
       <c r="K12" t="n">
-        <v>1224797</v>
+        <v>1235035</v>
       </c>
       <c r="L12" t="n">
-        <v>16.22</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="13">
@@ -1192,10 +1288,10 @@
         <v>1684968</v>
       </c>
       <c r="K13" t="n">
-        <v>1692471</v>
+        <v>1702849</v>
       </c>
       <c r="L13" t="n">
-        <v>14.61</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="14">
@@ -1232,10 +1328,10 @@
         <v>1392523</v>
       </c>
       <c r="K14" t="n">
-        <v>1403186</v>
+        <v>1410673</v>
       </c>
       <c r="L14" t="n">
-        <v>13.98</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="15">
@@ -1272,10 +1368,10 @@
         <v>1298219</v>
       </c>
       <c r="K15" t="n">
-        <v>1311274</v>
+        <v>1319798</v>
       </c>
       <c r="L15" t="n">
-        <v>12.54</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="16">
@@ -1312,10 +1408,10 @@
         <v>405803</v>
       </c>
       <c r="K16" t="n">
-        <v>407557</v>
+        <v>411446</v>
       </c>
       <c r="L16" t="n">
-        <v>13.04</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="17">
@@ -1352,10 +1448,10 @@
         <v>782232</v>
       </c>
       <c r="K17" t="n">
-        <v>788180</v>
+        <v>793558</v>
       </c>
       <c r="L17" t="n">
-        <v>12.71</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="18">
@@ -1392,10 +1488,10 @@
         <v>1124231</v>
       </c>
       <c r="K18" t="n">
-        <v>1136700</v>
+        <v>1140735</v>
       </c>
       <c r="L18" t="n">
-        <v>12.24</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="19">
@@ -1432,10 +1528,10 @@
         <v>994157</v>
       </c>
       <c r="K19" t="n">
-        <v>1002611</v>
+        <v>1006660</v>
       </c>
       <c r="L19" t="n">
-        <v>12.26</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="20">
@@ -1472,10 +1568,10 @@
         <v>796138</v>
       </c>
       <c r="K20" t="n">
-        <v>796622</v>
+        <v>799068</v>
       </c>
       <c r="L20" t="n">
-        <v>12.74</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="21">
@@ -1512,10 +1608,10 @@
         <v>3593561</v>
       </c>
       <c r="K21" t="n">
-        <v>3596978</v>
+        <v>3621556</v>
       </c>
       <c r="L21" t="n">
-        <v>12.42</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="22">
@@ -1552,10 +1648,10 @@
         <v>1041388</v>
       </c>
       <c r="K22" t="n">
-        <v>1049549</v>
+        <v>1056833</v>
       </c>
       <c r="L22" t="n">
-        <v>11.82</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="23">
@@ -1592,10 +1688,10 @@
         <v>1330905</v>
       </c>
       <c r="K23" t="n">
-        <v>1343780</v>
+        <v>1352497</v>
       </c>
       <c r="L23" t="n">
-        <v>11.56</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="24">
@@ -1632,10 +1728,10 @@
         <v>828037</v>
       </c>
       <c r="K24" t="n">
-        <v>834676</v>
+        <v>839436</v>
       </c>
       <c r="L24" t="n">
-        <v>11.07</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="25">
@@ -1672,10 +1768,10 @@
         <v>944623</v>
       </c>
       <c r="K25" t="n">
-        <v>951396</v>
+        <v>954806</v>
       </c>
       <c r="L25" t="n">
-        <v>11.04</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="26">
@@ -1712,10 +1808,10 @@
         <v>1375517</v>
       </c>
       <c r="K26" t="n">
-        <v>1385729</v>
+        <v>1395102</v>
       </c>
       <c r="L26" t="n">
-        <v>10.18</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="27">
@@ -1752,10 +1848,10 @@
         <v>1408364</v>
       </c>
       <c r="K27" t="n">
-        <v>1419356</v>
+        <v>1424651</v>
       </c>
       <c r="L27" t="n">
-        <v>9.93</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="28">
@@ -1792,10 +1888,10 @@
         <v>2061786</v>
       </c>
       <c r="K28" t="n">
-        <v>2071164</v>
+        <v>2088822</v>
       </c>
       <c r="L28" t="n">
-        <v>9.91</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1832,10 +1928,10 @@
         <v>863516</v>
       </c>
       <c r="K29" t="n">
-        <v>867700</v>
+        <v>871977</v>
       </c>
       <c r="L29" t="n">
-        <v>9.640000000000001</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="30">
@@ -1872,10 +1968,10 @@
         <v>791949</v>
       </c>
       <c r="K30" t="n">
-        <v>797763</v>
+        <v>800155</v>
       </c>
       <c r="L30" t="n">
-        <v>9.369999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="31">
@@ -1912,10 +2008,10 @@
         <v>1297789</v>
       </c>
       <c r="K31" t="n">
-        <v>1306922</v>
+        <v>1314852</v>
       </c>
       <c r="L31" t="n">
-        <v>9.279999999999999</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1952,10 +2048,10 @@
         <v>1646387</v>
       </c>
       <c r="K32" t="n">
-        <v>1650894</v>
+        <v>1669255</v>
       </c>
       <c r="L32" t="n">
-        <v>8.48</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="33">
@@ -1992,10 +2088,10 @@
         <v>1123022</v>
       </c>
       <c r="K33" t="n">
-        <v>1127142</v>
+        <v>1137078</v>
       </c>
       <c r="L33" t="n">
-        <v>8.369999999999999</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="34">
@@ -2032,10 +2128,10 @@
         <v>1220281</v>
       </c>
       <c r="K34" t="n">
-        <v>1225759</v>
+        <v>1231128</v>
       </c>
       <c r="L34" t="n">
-        <v>8.210000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="35">
@@ -2072,10 +2168,10 @@
         <v>1000545</v>
       </c>
       <c r="K35" t="n">
-        <v>1003699</v>
+        <v>1012948</v>
       </c>
       <c r="L35" t="n">
-        <v>5.66</v>
+        <v>4.79</v>
       </c>
     </row>
   </sheetData>
@@ -5011,7 +5107,2413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>men</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>third</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BELGAUM</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1818901</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1802493</v>
+      </c>
+      <c r="D2" t="n">
+        <v>162</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3621556</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BAGALKOT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>701908</v>
+      </c>
+      <c r="C3" t="n">
+        <v>708689</v>
+      </c>
+      <c r="D3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1410673</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>866502</v>
+      </c>
+      <c r="C4" t="n">
+        <v>836165</v>
+      </c>
+      <c r="D4" t="n">
+        <v>182</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1702849</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GULBARGA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>949607</v>
+      </c>
+      <c r="C5" t="n">
+        <v>919465</v>
+      </c>
+      <c r="D5" t="n">
+        <v>209</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1869281</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YADGIR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>442913</v>
+      </c>
+      <c r="C6" t="n">
+        <v>438656</v>
+      </c>
+      <c r="D6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E6" t="n">
+        <v>881633</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BIDAR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>639004</v>
+      </c>
+      <c r="C7" t="n">
+        <v>596001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1235035</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RAICHUR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>703856</v>
+      </c>
+      <c r="C8" t="n">
+        <v>716278</v>
+      </c>
+      <c r="D8" t="n">
+        <v>133</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1420267</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KOPPAL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>526350</v>
+      </c>
+      <c r="C9" t="n">
+        <v>530419</v>
+      </c>
+      <c r="D9" t="n">
+        <v>64</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1056833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GADAG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>397872</v>
+      </c>
+      <c r="C10" t="n">
+        <v>395643</v>
+      </c>
+      <c r="D10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E10" t="n">
+        <v>793558</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DHARWAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>682298</v>
+      </c>
+      <c r="C11" t="n">
+        <v>685345</v>
+      </c>
+      <c r="D11" t="n">
+        <v>66</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1367709</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UTTARA KANNADA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>568781</v>
+      </c>
+      <c r="C12" t="n">
+        <v>568293</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1137078</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HAVERI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>627342</v>
+      </c>
+      <c r="C13" t="n">
+        <v>603759</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1231128</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VIJAYANAGARA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>505047</v>
+      </c>
+      <c r="C14" t="n">
+        <v>501508</v>
+      </c>
+      <c r="D14" t="n">
+        <v>105</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1006660</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BELLARY</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>500256</v>
+      </c>
+      <c r="C15" t="n">
+        <v>518301</v>
+      </c>
+      <c r="D15" t="n">
+        <v>201</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1018758</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CHITRADURGA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>654290</v>
+      </c>
+      <c r="C16" t="n">
+        <v>660494</v>
+      </c>
+      <c r="D16" t="n">
+        <v>68</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1314852</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DAVANGERE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>656564</v>
+      </c>
+      <c r="C17" t="n">
+        <v>663154</v>
+      </c>
+      <c r="D17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1319798</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SHIMOGA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>666356</v>
+      </c>
+      <c r="C18" t="n">
+        <v>686116</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1352497</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UDUPI</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>490439</v>
+      </c>
+      <c r="C19" t="n">
+        <v>522498</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1012948</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHIKKMAGALUR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>428703</v>
+      </c>
+      <c r="C20" t="n">
+        <v>443257</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" t="n">
+        <v>871977</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TUMKUR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1034131</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1054634</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2088822</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHIKKABALLAPUR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>473037</v>
+      </c>
+      <c r="C22" t="n">
+        <v>481726</v>
+      </c>
+      <c r="D22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E22" t="n">
+        <v>954806</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KOLAR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>566073</v>
+      </c>
+      <c r="C23" t="n">
+        <v>574571</v>
+      </c>
+      <c r="D23" t="n">
+        <v>91</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1140735</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BANGALORE URBAN</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1135920</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1181183</v>
+      </c>
+      <c r="D24" t="n">
+        <v>267</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2317370</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BANGALORE RURAL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>392928</v>
+      </c>
+      <c r="C25" t="n">
+        <v>406080</v>
+      </c>
+      <c r="D25" t="n">
+        <v>60</v>
+      </c>
+      <c r="E25" t="n">
+        <v>799068</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B.B.M.P(NORTH)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>624168</v>
+      </c>
+      <c r="C26" t="n">
+        <v>670558</v>
+      </c>
+      <c r="D26" t="n">
+        <v>191</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1294917</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B.B.M.P(CENTRAL)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>505634</v>
+      </c>
+      <c r="C27" t="n">
+        <v>542414</v>
+      </c>
+      <c r="D27" t="n">
+        <v>143</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1048191</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B.B.M.P(SOUTH)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>527675</v>
+      </c>
+      <c r="C28" t="n">
+        <v>561372</v>
+      </c>
+      <c r="D28" t="n">
+        <v>86</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1089133</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RAMANAGARAM</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>410020</v>
+      </c>
+      <c r="C29" t="n">
+        <v>429379</v>
+      </c>
+      <c r="D29" t="n">
+        <v>37</v>
+      </c>
+      <c r="E29" t="n">
+        <v>839436</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDYA</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>698448</v>
+      </c>
+      <c r="C30" t="n">
+        <v>726116</v>
+      </c>
+      <c r="D30" t="n">
+        <v>87</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1424651</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HASSAN</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>689263</v>
+      </c>
+      <c r="C31" t="n">
+        <v>705807</v>
+      </c>
+      <c r="D31" t="n">
+        <v>32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1395102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DAKSHINA KANNADA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>818570</v>
+      </c>
+      <c r="C32" t="n">
+        <v>850667</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1669255</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>KODAGU</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>200843</v>
+      </c>
+      <c r="C33" t="n">
+        <v>210599</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>411446</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MYSORE</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1107549</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1155528</v>
+      </c>
+      <c r="D34" t="n">
+        <v>139</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2263216</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHAMARAJNAGAR</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>392174</v>
+      </c>
+      <c r="C35" t="n">
+        <v>407945</v>
+      </c>
+      <c r="D35" t="n">
+        <v>36</v>
+      </c>
+      <c r="E35" t="n">
+        <v>800155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>polling_stations</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>notices_generated</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>notices_delivered</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>notices_undelivered</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>hearings_held</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>hearings_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BELGAUM</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4644</v>
+      </c>
+      <c r="C2" t="n">
+        <v>84412</v>
+      </c>
+      <c r="D2" t="n">
+        <v>81160</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3252</v>
+      </c>
+      <c r="F2" t="n">
+        <v>74565</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6595</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BAGALKOT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1855</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47433</v>
+      </c>
+      <c r="D3" t="n">
+        <v>47433</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2159</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24532</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24532</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24252</v>
+      </c>
+      <c r="G4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GULBARGA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2461</v>
+      </c>
+      <c r="C5" t="n">
+        <v>105511</v>
+      </c>
+      <c r="D5" t="n">
+        <v>104131</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F5" t="n">
+        <v>83952</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20179</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YADGIR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1162</v>
+      </c>
+      <c r="C6" t="n">
+        <v>55083</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55083</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54647</v>
+      </c>
+      <c r="G6" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BIDAR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C7" t="n">
+        <v>32673</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32673</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>27811</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4862</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RAICHUR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1892</v>
+      </c>
+      <c r="C8" t="n">
+        <v>69099</v>
+      </c>
+      <c r="D8" t="n">
+        <v>69099</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>66094</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KOPPAL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1352</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14401</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14401</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14401</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GADAG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>983</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25973</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25965</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24853</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DHARWAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1707</v>
+      </c>
+      <c r="C11" t="n">
+        <v>47978</v>
+      </c>
+      <c r="D11" t="n">
+        <v>47978</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45009</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UTTARA KANNADA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C12" t="n">
+        <v>65248</v>
+      </c>
+      <c r="D12" t="n">
+        <v>65248</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>63499</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HAVERI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1559</v>
+      </c>
+      <c r="C13" t="n">
+        <v>60011</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60011</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57102</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VIJAYANAGARA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1301</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30622</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30622</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>29474</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BELLARY</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37868</v>
+      </c>
+      <c r="D15" t="n">
+        <v>37868</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36998</v>
+      </c>
+      <c r="G15" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CHITRADURGA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1764</v>
+      </c>
+      <c r="C16" t="n">
+        <v>68750</v>
+      </c>
+      <c r="D16" t="n">
+        <v>68750</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>68736</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DAVANGERE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7086</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7086</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6984</v>
+      </c>
+      <c r="G17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SHIMOGA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1886</v>
+      </c>
+      <c r="C18" t="n">
+        <v>48660</v>
+      </c>
+      <c r="D18" t="n">
+        <v>48660</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45273</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3387</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UDUPI</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C19" t="n">
+        <v>97675</v>
+      </c>
+      <c r="D19" t="n">
+        <v>97675</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>93271</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHIKKMAGALUR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C20" t="n">
+        <v>91610</v>
+      </c>
+      <c r="D20" t="n">
+        <v>91610</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>87794</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TUMKUR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2745</v>
+      </c>
+      <c r="C21" t="n">
+        <v>111876</v>
+      </c>
+      <c r="D21" t="n">
+        <v>111875</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>105798</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6077</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHIKKABALLAPUR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1361</v>
+      </c>
+      <c r="C22" t="n">
+        <v>55798</v>
+      </c>
+      <c r="D22" t="n">
+        <v>55798</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51286</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KOLAR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1578</v>
+      </c>
+      <c r="C23" t="n">
+        <v>142182</v>
+      </c>
+      <c r="D23" t="n">
+        <v>142182</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>140978</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BANGALORE URBAN</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3354</v>
+      </c>
+      <c r="C24" t="n">
+        <v>945775</v>
+      </c>
+      <c r="D24" t="n">
+        <v>943582</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2193</v>
+      </c>
+      <c r="F24" t="n">
+        <v>888639</v>
+      </c>
+      <c r="G24" t="n">
+        <v>54943</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BANGALORE RURAL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1154</v>
+      </c>
+      <c r="C25" t="n">
+        <v>56349</v>
+      </c>
+      <c r="D25" t="n">
+        <v>55942</v>
+      </c>
+      <c r="E25" t="n">
+        <v>407</v>
+      </c>
+      <c r="F25" t="n">
+        <v>48128</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7814</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B.B.M.P(NORTH)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2086</v>
+      </c>
+      <c r="C26" t="n">
+        <v>613666</v>
+      </c>
+      <c r="D26" t="n">
+        <v>613661</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>583367</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30294</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B.B.M.P(CENTRAL)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1673</v>
+      </c>
+      <c r="C27" t="n">
+        <v>429391</v>
+      </c>
+      <c r="D27" t="n">
+        <v>428335</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F27" t="n">
+        <v>397036</v>
+      </c>
+      <c r="G27" t="n">
+        <v>31299</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B.B.M.P(SOUTH)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1895</v>
+      </c>
+      <c r="C28" t="n">
+        <v>418213</v>
+      </c>
+      <c r="D28" t="n">
+        <v>417945</v>
+      </c>
+      <c r="E28" t="n">
+        <v>268</v>
+      </c>
+      <c r="F28" t="n">
+        <v>352610</v>
+      </c>
+      <c r="G28" t="n">
+        <v>65335</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RAMANAGARAM</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1183</v>
+      </c>
+      <c r="C29" t="n">
+        <v>19696</v>
+      </c>
+      <c r="D29" t="n">
+        <v>19696</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>19196</v>
+      </c>
+      <c r="G29" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDYA</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1889</v>
+      </c>
+      <c r="C30" t="n">
+        <v>150259</v>
+      </c>
+      <c r="D30" t="n">
+        <v>150259</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>147068</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HASSAN</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C31" t="n">
+        <v>79774</v>
+      </c>
+      <c r="D31" t="n">
+        <v>79774</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>74601</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5173</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DAKSHINA KANNADA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C32" t="n">
+        <v>150131</v>
+      </c>
+      <c r="D32" t="n">
+        <v>150131</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>141968</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8163</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>KODAGU</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>567</v>
+      </c>
+      <c r="C33" t="n">
+        <v>58883</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58883</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>57881</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MYSORE</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2967</v>
+      </c>
+      <c r="C34" t="n">
+        <v>128217</v>
+      </c>
+      <c r="D34" t="n">
+        <v>128217</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>121515</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6702</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHAMARAJNAGAR</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7480</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7480</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7054</v>
+      </c>
+      <c r="G35" t="n">
+        <v>426</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>form6</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>form6a</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>form7</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>form8</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>all_forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BELGAUM</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>51934</v>
+      </c>
+      <c r="C2" t="n">
+        <v>57</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4789</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60564</v>
+      </c>
+      <c r="F2" t="n">
+        <v>117344</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BAGALKOT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20197</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3083</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24901</v>
+      </c>
+      <c r="F3" t="n">
+        <v>48188</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>28994</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4229</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28691</v>
+      </c>
+      <c r="F4" t="n">
+        <v>61926</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GULBARGA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>52076</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1217</v>
+      </c>
+      <c r="E5" t="n">
+        <v>49949</v>
+      </c>
+      <c r="F5" t="n">
+        <v>103303</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YADGIR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>22515</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15041</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38359</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BIDAR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32444</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6101</v>
+      </c>
+      <c r="E7" t="n">
+        <v>28854</v>
+      </c>
+      <c r="F7" t="n">
+        <v>67415</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RAICHUR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>34875</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25859</v>
+      </c>
+      <c r="F8" t="n">
+        <v>64471</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KOPPAL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17250</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3092</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19085</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39428</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GADAG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>13686</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1849</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15228</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30771</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DHARWAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>25453</v>
+      </c>
+      <c r="C11" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2522</v>
+      </c>
+      <c r="E11" t="n">
+        <v>38139</v>
+      </c>
+      <c r="F11" t="n">
+        <v>66190</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UTTARA KANNADA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>18729</v>
+      </c>
+      <c r="C12" t="n">
+        <v>65</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2270</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20028</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41092</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HAVERI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>13712</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2230</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18235</v>
+      </c>
+      <c r="F13" t="n">
+        <v>34188</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VIJAYANAGARA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>14930</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2746</v>
+      </c>
+      <c r="E14" t="n">
+        <v>40726</v>
+      </c>
+      <c r="F14" t="n">
+        <v>58409</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BELLARY</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13974</v>
+      </c>
+      <c r="C15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2270</v>
+      </c>
+      <c r="E15" t="n">
+        <v>23307</v>
+      </c>
+      <c r="F15" t="n">
+        <v>39579</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CHITRADURGA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>19962</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3603</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21866</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45442</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DAVANGERE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>22889</v>
+      </c>
+      <c r="C17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4736</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28693</v>
+      </c>
+      <c r="F17" t="n">
+        <v>56341</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SHIMOGA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>23644</v>
+      </c>
+      <c r="C18" t="n">
+        <v>57</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6987</v>
+      </c>
+      <c r="E18" t="n">
+        <v>33866</v>
+      </c>
+      <c r="F18" t="n">
+        <v>64554</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UDUPI</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>16064</v>
+      </c>
+      <c r="C19" t="n">
+        <v>354</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2712</v>
+      </c>
+      <c r="E19" t="n">
+        <v>39458</v>
+      </c>
+      <c r="F19" t="n">
+        <v>58588</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHIKKMAGALUR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14952</v>
+      </c>
+      <c r="C20" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3144</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20272</v>
+      </c>
+      <c r="F20" t="n">
+        <v>38410</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TUMKUR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>35712</v>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5975</v>
+      </c>
+      <c r="E21" t="n">
+        <v>38679</v>
+      </c>
+      <c r="F21" t="n">
+        <v>80399</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHIKKABALLAPUR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12928</v>
+      </c>
+      <c r="C22" t="n">
+        <v>13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2065</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15977</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30983</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KOLAR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>18404</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2935</v>
+      </c>
+      <c r="E23" t="n">
+        <v>24886</v>
+      </c>
+      <c r="F23" t="n">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BANGALORE URBAN</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>115216</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1411</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5177</v>
+      </c>
+      <c r="E24" t="n">
+        <v>135068</v>
+      </c>
+      <c r="F24" t="n">
+        <v>256872</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BANGALORE RURAL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>14734</v>
+      </c>
+      <c r="C25" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1769</v>
+      </c>
+      <c r="E25" t="n">
+        <v>19314</v>
+      </c>
+      <c r="F25" t="n">
+        <v>35843</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B.B.M.P(NORTH)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>59366</v>
+      </c>
+      <c r="C26" t="n">
+        <v>795</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3321</v>
+      </c>
+      <c r="E26" t="n">
+        <v>78201</v>
+      </c>
+      <c r="F26" t="n">
+        <v>141683</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B.B.M.P(CENTRAL)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>44852</v>
+      </c>
+      <c r="C27" t="n">
+        <v>363</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2212</v>
+      </c>
+      <c r="E27" t="n">
+        <v>57481</v>
+      </c>
+      <c r="F27" t="n">
+        <v>104908</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B.B.M.P(SOUTH)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>41885</v>
+      </c>
+      <c r="C28" t="n">
+        <v>384</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2245</v>
+      </c>
+      <c r="E28" t="n">
+        <v>63040</v>
+      </c>
+      <c r="F28" t="n">
+        <v>107554</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RAMANAGARAM</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>15874</v>
+      </c>
+      <c r="C29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2475</v>
+      </c>
+      <c r="E29" t="n">
+        <v>21412</v>
+      </c>
+      <c r="F29" t="n">
+        <v>39786</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDYA</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>19450</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3207</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26684</v>
+      </c>
+      <c r="F30" t="n">
+        <v>49351</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HASSAN</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>23627</v>
+      </c>
+      <c r="C31" t="n">
+        <v>28</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3372</v>
+      </c>
+      <c r="E31" t="n">
+        <v>28376</v>
+      </c>
+      <c r="F31" t="n">
+        <v>55403</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DAKSHINA KANNADA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>35786</v>
+      </c>
+      <c r="C32" t="n">
+        <v>582</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6762</v>
+      </c>
+      <c r="E32" t="n">
+        <v>67866</v>
+      </c>
+      <c r="F32" t="n">
+        <v>110996</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>KODAGU</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6599</v>
+      </c>
+      <c r="C33" t="n">
+        <v>22</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1549</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19882</v>
+      </c>
+      <c r="F33" t="n">
+        <v>28052</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MYSORE</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>41094</v>
+      </c>
+      <c r="C34" t="n">
+        <v>160</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3561</v>
+      </c>
+      <c r="E34" t="n">
+        <v>68524</v>
+      </c>
+      <c r="F34" t="n">
+        <v>113339</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHAMARAJNAGAR</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8690</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1924</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16200</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26815</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5214,12 +7716,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roll_25_sep_2026</t>
+          <t>roll_9_oct_2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Electors on the roll of 25 September 2026, published while claims and objections were being heard.</t>
+          <t>Electors on the roll of 9 October 2026, published while notices were being heard. The final roll is due on 27 October 2026.</t>
         </is>
       </c>
     </row>
@@ -5628,6 +8130,312 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>Total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Roll of 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>District.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Roll of 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>men</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Men on the roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Roll of 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Women on the roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Roll of 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>third</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Third-gender electors on the roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Roll of 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>District.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>polling_stations</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Polling stations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>notices_generated</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Notices generated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>notices_delivered</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Notices delivered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>notices_undelivered</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Notices not delivered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>hearings_held</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hearings held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Notices to 9 October 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>hearings_pending</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hearings pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>District.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>form6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Form 6 received (to add a name).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>form6a</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Form 6A received (overseas electors).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>form7</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Form 7 received (objection to a name).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>form8</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Form 8 received (correction or shift).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Forms 6, 6A, 7 and 8 to 8 Octob</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>all_forms</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>All four forms received.</t>
         </is>
       </c>
     </row>

--- a/downloads/karnataka.xlsx
+++ b/downloads/karnataka.xlsx
@@ -827,7 +827,7 @@
         <v>1058028</v>
       </c>
       <c r="D2" t="n">
-        <v>49.33</v>
+        <v>49.3303</v>
       </c>
       <c r="E2" t="n">
         <v>266552</v>
@@ -851,7 +851,7 @@
         <v>1089133</v>
       </c>
       <c r="L2" t="n">
-        <v>49.22</v>
+        <v>49.2195</v>
       </c>
     </row>
     <row r="3">
@@ -867,7 +867,7 @@
         <v>860723</v>
       </c>
       <c r="D3" t="n">
-        <v>45.54</v>
+        <v>45.5429</v>
       </c>
       <c r="E3" t="n">
         <v>146441</v>
@@ -891,7 +891,7 @@
         <v>1048191</v>
       </c>
       <c r="L3" t="n">
-        <v>44.54</v>
+        <v>44.5378</v>
       </c>
     </row>
     <row r="4">
@@ -907,7 +907,7 @@
         <v>1052536</v>
       </c>
       <c r="D4" t="n">
-        <v>45.12</v>
+        <v>45.1225</v>
       </c>
       <c r="E4" t="n">
         <v>106373</v>
@@ -931,7 +931,7 @@
         <v>1294917</v>
       </c>
       <c r="L4" t="n">
-        <v>44.49</v>
+        <v>44.4866</v>
       </c>
     </row>
     <row r="5">
@@ -947,7 +947,7 @@
         <v>1717416</v>
       </c>
       <c r="D5" t="n">
-        <v>42.71</v>
+        <v>42.7108</v>
       </c>
       <c r="E5" t="n">
         <v>207892</v>
@@ -971,7 +971,7 @@
         <v>2317370</v>
       </c>
       <c r="L5" t="n">
-        <v>42.37</v>
+        <v>42.3689</v>
       </c>
     </row>
     <row r="6">
@@ -987,7 +987,7 @@
         <v>521957</v>
       </c>
       <c r="D6" t="n">
-        <v>22.01</v>
+        <v>22.0092</v>
       </c>
       <c r="E6" t="n">
         <v>47445</v>
@@ -1011,7 +1011,7 @@
         <v>1869281</v>
       </c>
       <c r="L6" t="n">
-        <v>21.18</v>
+        <v>21.1787</v>
       </c>
     </row>
     <row r="7">
@@ -1027,7 +1027,7 @@
         <v>557241</v>
       </c>
       <c r="D7" t="n">
-        <v>19.9</v>
+        <v>19.9036</v>
       </c>
       <c r="E7" t="n">
         <v>134287</v>
@@ -1051,7 +1051,7 @@
         <v>2263216</v>
       </c>
       <c r="L7" t="n">
-        <v>19.16</v>
+        <v>19.162</v>
       </c>
     </row>
     <row r="8">
@@ -1067,7 +1067,7 @@
         <v>321396</v>
       </c>
       <c r="D8" t="n">
-        <v>18.75</v>
+        <v>18.7451</v>
       </c>
       <c r="E8" t="n">
         <v>30733</v>
@@ -1091,7 +1091,7 @@
         <v>1420267</v>
       </c>
       <c r="L8" t="n">
-        <v>17.16</v>
+        <v>17.1643</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>223279</v>
       </c>
       <c r="D9" t="n">
-        <v>18.16</v>
+        <v>18.1589</v>
       </c>
       <c r="E9" t="n">
         <v>49700</v>
@@ -1131,7 +1131,7 @@
         <v>1018758</v>
       </c>
       <c r="L9" t="n">
-        <v>17.15</v>
+        <v>17.1463</v>
       </c>
     </row>
     <row r="10">
@@ -1147,7 +1147,7 @@
         <v>189231</v>
       </c>
       <c r="D10" t="n">
-        <v>17.97</v>
+        <v>17.9666</v>
       </c>
       <c r="E10" t="n">
         <v>17306</v>
@@ -1171,7 +1171,7 @@
         <v>881633</v>
       </c>
       <c r="L10" t="n">
-        <v>16.29</v>
+        <v>16.2929</v>
       </c>
     </row>
     <row r="11">
@@ -1187,7 +1187,7 @@
         <v>268015</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52</v>
+        <v>16.5241</v>
       </c>
       <c r="E11" t="n">
         <v>62079</v>
@@ -1211,7 +1211,7 @@
         <v>1367709</v>
       </c>
       <c r="L11" t="n">
-        <v>15.68</v>
+        <v>15.6756</v>
       </c>
     </row>
     <row r="12">
@@ -1227,7 +1227,7 @@
         <v>241043</v>
       </c>
       <c r="D12" t="n">
-        <v>16.49</v>
+        <v>16.4877</v>
       </c>
       <c r="E12" t="n">
         <v>20911</v>
@@ -1251,7 +1251,7 @@
         <v>1235035</v>
       </c>
       <c r="L12" t="n">
-        <v>15.52</v>
+        <v>15.5219</v>
       </c>
     </row>
     <row r="13">
@@ -1267,7 +1267,7 @@
         <v>297146</v>
       </c>
       <c r="D13" t="n">
-        <v>14.99</v>
+        <v>14.9914</v>
       </c>
       <c r="E13" t="n">
         <v>59092</v>
@@ -1291,7 +1291,7 @@
         <v>1702849</v>
       </c>
       <c r="L13" t="n">
-        <v>14.09</v>
+        <v>14.0893</v>
       </c>
     </row>
     <row r="14">
@@ -1307,7 +1307,7 @@
         <v>238679</v>
       </c>
       <c r="D14" t="n">
-        <v>14.63</v>
+        <v>14.6321</v>
       </c>
       <c r="E14" t="n">
         <v>20869</v>
@@ -1331,87 +1331,87 @@
         <v>1410673</v>
       </c>
       <c r="L14" t="n">
-        <v>13.52</v>
+        <v>13.5194</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Davangere</t>
+          <t>Kodagu</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1499282</v>
+        <v>468657</v>
       </c>
       <c r="C15" t="n">
-        <v>201063</v>
+        <v>62854</v>
       </c>
       <c r="D15" t="n">
-        <v>13.41</v>
+        <v>13.4115</v>
       </c>
       <c r="E15" t="n">
-        <v>31685</v>
+        <v>9580</v>
       </c>
       <c r="F15" t="n">
-        <v>105001</v>
+        <v>33381</v>
       </c>
       <c r="G15" t="n">
-        <v>34700</v>
+        <v>13731</v>
       </c>
       <c r="H15" t="n">
-        <v>28333</v>
+        <v>6046</v>
       </c>
       <c r="I15" t="n">
-        <v>1344</v>
+        <v>116</v>
       </c>
       <c r="J15" t="n">
-        <v>1298219</v>
+        <v>405803</v>
       </c>
       <c r="K15" t="n">
-        <v>1319798</v>
+        <v>411446</v>
       </c>
       <c r="L15" t="n">
-        <v>11.97</v>
+        <v>12.2074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kodagu</t>
+          <t>Davangere</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>468657</v>
+        <v>1499282</v>
       </c>
       <c r="C16" t="n">
-        <v>62854</v>
+        <v>201063</v>
       </c>
       <c r="D16" t="n">
-        <v>13.41</v>
+        <v>13.4106</v>
       </c>
       <c r="E16" t="n">
-        <v>9580</v>
+        <v>31685</v>
       </c>
       <c r="F16" t="n">
-        <v>33381</v>
+        <v>105001</v>
       </c>
       <c r="G16" t="n">
-        <v>13731</v>
+        <v>34700</v>
       </c>
       <c r="H16" t="n">
-        <v>6046</v>
+        <v>28333</v>
       </c>
       <c r="I16" t="n">
-        <v>116</v>
+        <v>1344</v>
       </c>
       <c r="J16" t="n">
-        <v>405803</v>
+        <v>1298219</v>
       </c>
       <c r="K16" t="n">
-        <v>411446</v>
+        <v>1319798</v>
       </c>
       <c r="L16" t="n">
-        <v>12.21</v>
+        <v>11.9713</v>
       </c>
     </row>
     <row r="17">
@@ -1427,7 +1427,7 @@
         <v>120715</v>
       </c>
       <c r="D17" t="n">
-        <v>13.37</v>
+        <v>13.369</v>
       </c>
       <c r="E17" t="n">
         <v>5192</v>
@@ -1451,7 +1451,7 @@
         <v>793558</v>
       </c>
       <c r="L17" t="n">
-        <v>12.11</v>
+        <v>12.1147</v>
       </c>
     </row>
     <row r="18">
@@ -1467,7 +1467,7 @@
         <v>171034</v>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.2046</v>
       </c>
       <c r="E18" t="n">
         <v>37527</v>
@@ -1491,7 +1491,7 @@
         <v>1140735</v>
       </c>
       <c r="L18" t="n">
-        <v>11.93</v>
+        <v>11.9304</v>
       </c>
     </row>
     <row r="19">
@@ -1507,7 +1507,7 @@
         <v>148575</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>13.0017</v>
       </c>
       <c r="E19" t="n">
         <v>21224</v>
@@ -1531,7 +1531,7 @@
         <v>1006660</v>
       </c>
       <c r="L19" t="n">
-        <v>11.91</v>
+        <v>11.9076</v>
       </c>
     </row>
     <row r="20">
@@ -1547,7 +1547,7 @@
         <v>116775</v>
       </c>
       <c r="D20" t="n">
-        <v>12.79</v>
+        <v>12.7915</v>
       </c>
       <c r="E20" t="n">
         <v>13607</v>
@@ -1571,87 +1571,87 @@
         <v>799068</v>
       </c>
       <c r="L20" t="n">
-        <v>12.47</v>
+        <v>12.4705</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Belgaum</t>
+          <t>Koppal</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4107000</v>
+        <v>1190214</v>
       </c>
       <c r="C21" t="n">
-        <v>513439</v>
+        <v>148826</v>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>12.5041</v>
       </c>
       <c r="E21" t="n">
-        <v>26459</v>
+        <v>11332</v>
       </c>
       <c r="F21" t="n">
-        <v>283249</v>
+        <v>76071</v>
       </c>
       <c r="G21" t="n">
-        <v>134903</v>
+        <v>28922</v>
       </c>
       <c r="H21" t="n">
-        <v>68606</v>
+        <v>32501</v>
       </c>
       <c r="I21" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3593561</v>
+        <v>1041388</v>
       </c>
       <c r="K21" t="n">
-        <v>3621556</v>
+        <v>1056833</v>
       </c>
       <c r="L21" t="n">
-        <v>11.82</v>
+        <v>11.2065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Koppal</t>
+          <t>Belgaum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1190214</v>
+        <v>4107000</v>
       </c>
       <c r="C22" t="n">
-        <v>148826</v>
+        <v>513439</v>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>12.5016</v>
       </c>
       <c r="E22" t="n">
-        <v>11332</v>
+        <v>26459</v>
       </c>
       <c r="F22" t="n">
-        <v>76071</v>
+        <v>283249</v>
       </c>
       <c r="G22" t="n">
-        <v>28922</v>
+        <v>134903</v>
       </c>
       <c r="H22" t="n">
-        <v>32501</v>
+        <v>68606</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="J22" t="n">
-        <v>1041388</v>
+        <v>3593561</v>
       </c>
       <c r="K22" t="n">
-        <v>1056833</v>
+        <v>3621556</v>
       </c>
       <c r="L22" t="n">
-        <v>11.21</v>
+        <v>11.8199</v>
       </c>
     </row>
     <row r="23">
@@ -1667,7 +1667,7 @@
         <v>188554</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41</v>
+        <v>12.4093</v>
       </c>
       <c r="E23" t="n">
         <v>23165</v>
@@ -1691,7 +1691,7 @@
         <v>1352497</v>
       </c>
       <c r="L23" t="n">
-        <v>10.99</v>
+        <v>10.9883</v>
       </c>
     </row>
     <row r="24">
@@ -1707,7 +1707,7 @@
         <v>110549</v>
       </c>
       <c r="D24" t="n">
-        <v>11.78</v>
+        <v>11.7782</v>
       </c>
       <c r="E24" t="n">
         <v>13061</v>
@@ -1731,7 +1731,7 @@
         <v>839436</v>
       </c>
       <c r="L24" t="n">
-        <v>10.56</v>
+        <v>10.5638</v>
       </c>
     </row>
     <row r="25">
@@ -1747,7 +1747,7 @@
         <v>124881</v>
       </c>
       <c r="D25" t="n">
-        <v>11.68</v>
+        <v>11.6765</v>
       </c>
       <c r="E25" t="n">
         <v>7844</v>
@@ -1771,7 +1771,7 @@
         <v>954806</v>
       </c>
       <c r="L25" t="n">
-        <v>10.72</v>
+        <v>10.7244</v>
       </c>
     </row>
     <row r="26">
@@ -1787,7 +1787,7 @@
         <v>167285</v>
       </c>
       <c r="D26" t="n">
-        <v>10.84</v>
+        <v>10.8429</v>
       </c>
       <c r="E26" t="n">
         <v>24632</v>
@@ -1811,7 +1811,7 @@
         <v>1395102</v>
       </c>
       <c r="L26" t="n">
-        <v>9.57</v>
+        <v>9.573499999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1827,7 +1827,7 @@
         <v>167485</v>
       </c>
       <c r="D27" t="n">
-        <v>10.63</v>
+        <v>10.6282</v>
       </c>
       <c r="E27" t="n">
         <v>23770</v>
@@ -1851,7 +1851,7 @@
         <v>1424651</v>
       </c>
       <c r="L27" t="n">
-        <v>9.59</v>
+        <v>9.5947</v>
       </c>
     </row>
     <row r="28">
@@ -1867,7 +1867,7 @@
         <v>237093</v>
       </c>
       <c r="D28" t="n">
-        <v>10.31</v>
+        <v>10.3134</v>
       </c>
       <c r="E28" t="n">
         <v>33021</v>
@@ -1891,7 +1891,7 @@
         <v>2088822</v>
       </c>
       <c r="L28" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1374</v>
       </c>
     </row>
     <row r="29">
@@ -1907,7 +1907,7 @@
         <v>96715</v>
       </c>
       <c r="D29" t="n">
-        <v>10.07</v>
+        <v>10.0721</v>
       </c>
       <c r="E29" t="n">
         <v>10772</v>
@@ -1931,7 +1931,7 @@
         <v>871977</v>
       </c>
       <c r="L29" t="n">
-        <v>9.19</v>
+        <v>9.190899999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1947,7 +1947,7 @@
         <v>88275</v>
       </c>
       <c r="D30" t="n">
-        <v>10.03</v>
+        <v>10.0287</v>
       </c>
       <c r="E30" t="n">
         <v>10311</v>
@@ -1971,7 +1971,7 @@
         <v>800155</v>
       </c>
       <c r="L30" t="n">
-        <v>9.1</v>
+        <v>9.096399999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1987,7 +1987,7 @@
         <v>142745</v>
       </c>
       <c r="D31" t="n">
-        <v>9.91</v>
+        <v>9.9092</v>
       </c>
       <c r="E31" t="n">
         <v>18837</v>
@@ -2011,7 +2011,7 @@
         <v>1314852</v>
       </c>
       <c r="L31" t="n">
-        <v>8.720000000000001</v>
+        <v>8.7247</v>
       </c>
     </row>
     <row r="32">
@@ -2027,7 +2027,7 @@
         <v>157379</v>
       </c>
       <c r="D32" t="n">
-        <v>8.73</v>
+        <v>8.725</v>
       </c>
       <c r="E32" t="n">
         <v>11124</v>
@@ -2051,7 +2051,7 @@
         <v>1669255</v>
       </c>
       <c r="L32" t="n">
-        <v>7.46</v>
+        <v>7.4572</v>
       </c>
     </row>
     <row r="33">
@@ -2067,7 +2067,7 @@
         <v>107015</v>
       </c>
       <c r="D33" t="n">
-        <v>8.699999999999999</v>
+        <v>8.700100000000001</v>
       </c>
       <c r="E33" t="n">
         <v>4649</v>
@@ -2091,7 +2091,7 @@
         <v>1137078</v>
       </c>
       <c r="L33" t="n">
-        <v>7.56</v>
+        <v>7.5574</v>
       </c>
     </row>
     <row r="34">
@@ -2107,7 +2107,7 @@
         <v>115061</v>
       </c>
       <c r="D34" t="n">
-        <v>8.619999999999999</v>
+        <v>8.6166</v>
       </c>
       <c r="E34" t="n">
         <v>5425</v>
@@ -2131,7 +2131,7 @@
         <v>1231128</v>
       </c>
       <c r="L34" t="n">
-        <v>7.8</v>
+        <v>7.8043</v>
       </c>
     </row>
     <row r="35">
@@ -2147,7 +2147,7 @@
         <v>63331</v>
       </c>
       <c r="D35" t="n">
-        <v>5.95</v>
+        <v>5.9529</v>
       </c>
       <c r="E35" t="n">
         <v>4145</v>
@@ -2171,7 +2171,7 @@
         <v>1012948</v>
       </c>
       <c r="L35" t="n">
-        <v>4.79</v>
+        <v>4.787</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/karnataka.xlsx
+++ b/downloads/karnataka.xlsx
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Electors on the roll of 9 October 2026, published while notices were being heard. The final roll is due on 27 October 2026.</t>
+          <t>Electors on the roll of 9 October 2026, published while notices were being heard. The final roll followed on 27 October 2026.</t>
         </is>
       </c>
     </row>
